--- a/assets/Clause_Domains.xlsx
+++ b/assets/Clause_Domains.xlsx
@@ -48,12 +48,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">شناخت سازمان و شرایط آن</t>
+          <t xml:space="preserve">شناخت سازمان، دامنه و ذینفعان</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organizational Context</t>
+          <t xml:space="preserve">Organizational Context, Scope &amp; Interested Parties</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -70,12 +70,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ذی‌نفعان و دامنه سیستم مدیریت امنیت اطلاعات</t>
+          <t xml:space="preserve">شناخت سازمان، دامنه و ذینفعان</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interested Parties &amp; ISMS Scope</t>
+          <t xml:space="preserve">Organizational Context, Scope &amp; Interested Parties</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -92,12 +92,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ذی‌نفعان و دامنه سیستم مدیریت امنیت اطلاعات</t>
+          <t xml:space="preserve">شناخت سازمان، دامنه و ذینفعان</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interested Parties &amp; ISMS Scope</t>
+          <t xml:space="preserve">Organizational Context, Scope &amp; Interested Parties</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -114,12 +114,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ذی‌نفعان و دامنه سیستم مدیریت امنیت اطلاعات</t>
+          <t xml:space="preserve">شناخت سازمان، دامنه و ذینفعان</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interested Parties &amp; ISMS Scope</t>
+          <t xml:space="preserve">Organizational Context, Scope &amp; Interested Parties</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -202,12 +202,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیریت ریسک و فرصت‌ها</t>
+          <t xml:space="preserve">مدیریت ریسک</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risk &amp; Opportunity Management</t>
+          <t xml:space="preserve">Risk Management</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -224,12 +224,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیریت ریسک امنیت اطلاعات</t>
+          <t xml:space="preserve">مدیریت ریسک</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Security Risk Management</t>
+          <t xml:space="preserve">Risk Management</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -246,12 +246,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیریت ریسک امنیت اطلاعات</t>
+          <t xml:space="preserve">مدیریت ریسک</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Security Risk Management</t>
+          <t xml:space="preserve">Risk Management</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -744,32 +744,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">شناخت سازمان و شرایط آن</t>
+          <t xml:space="preserve">شناخت سازمان، دامنه و ذینفعان</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organizational Context</t>
+          <t xml:space="preserve">Organizational Context, Scope &amp; Interested Parties</t>
         </is>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">interested-scope</t>
+          <t xml:space="preserve">leadership</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ذی‌نفعان و دامنه سیستم مدیریت امنیت اطلاعات</t>
+          <t xml:space="preserve">رهبری و حاکمیت</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interested Parties &amp; ISMS Scope</t>
+          <t xml:space="preserve">Leadership &amp; Governance</t>
         </is>
       </c>
       <c r="D3">
@@ -779,17 +779,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">leadership</t>
+          <t xml:space="preserve">risk-management</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">رهبری و حاکمیت</t>
+          <t xml:space="preserve">مدیریت ریسک</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leadership &amp; Governance</t>
+          <t xml:space="preserve">Risk Management</t>
         </is>
       </c>
       <c r="D4">
@@ -799,77 +799,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">risk-opportunity</t>
+          <t xml:space="preserve">objectives-change</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیریت ریسک و فرصت‌ها</t>
+          <t xml:space="preserve">اهداف و طرح‌ریزی تغییرات</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risk &amp; Opportunity Management</t>
+          <t xml:space="preserve">Objectives &amp; Change Planning</t>
         </is>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">security-risk</t>
+          <t xml:space="preserve">resources-awareness</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدیریت ریسک امنیت اطلاعات</t>
+          <t xml:space="preserve">منابع، شایستگی و آگاهی</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Security Risk Management</t>
+          <t xml:space="preserve">Resources, Competence &amp; Awareness</t>
         </is>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">objectives-change</t>
+          <t xml:space="preserve">communication-documentation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">اهداف و طرح‌ریزی تغییرات</t>
+          <t xml:space="preserve">ارتباطات و اطلاعات مدون</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objectives &amp; Change Planning</t>
+          <t xml:space="preserve">Communication &amp; Documented Information</t>
         </is>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">resources-awareness</t>
+          <t xml:space="preserve">operations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">منابع، شایستگی و آگاهی</t>
+          <t xml:space="preserve">کنترل عملیات</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resources, Competence &amp; Awareness</t>
+          <t xml:space="preserve">Operational Control</t>
         </is>
       </c>
       <c r="D8">
@@ -879,65 +879,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">communication-documentation</t>
+          <t xml:space="preserve">performance-improvement</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ارتباطات و اطلاعات مدون</t>
+          <t xml:space="preserve">ارزیابی عملکرد و بهبود</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication &amp; Documented Information</t>
+          <t xml:space="preserve">Performance Evaluation &amp; Improvement</t>
         </is>
       </c>
       <c r="D9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">operations</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کنترل عملیات</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operational Control</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">performance-improvement</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ارزیابی عملکرد و بهبود</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Performance Evaluation &amp; Improvement</t>
-        </is>
-      </c>
-      <c r="D11">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D11"/>
+  <autoFilter ref="A1:D9"/>
 </worksheet>
 </file>
 
@@ -1002,12 +962,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">فهرست صریح اقلام هر یک از ده حوزه در پیام کاربر</t>
+          <t xml:space="preserve">فهرست ده حوزهٔ کنترل و هشت حوزهٔ الزامات، با ادغام‌های درخواستی نسخهٔ ۱۴</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicit assignments in the user-provided mapping</t>
+          <t xml:space="preserve">User assignments with the version-14 requirements-domain merges</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
